--- a/CPI.xlsx
+++ b/CPI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kise-my.sharepoint.com/personal/sandar_aye_ki_se/Documents/Sandar_PhD project/5. Cost by state/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kise.sharepoint.com/teams/GRP_EconomicevaluationsofmalnutritioninSwedisholderadultsKIL/Delade dokument/Individal level data analysis/Data/Malnutrition statistical analysis/Malnutrition-study/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{05125B79-E365-6E46-8F3D-67F167C30EE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E72A5130-06E6-EE4F-AB15-7B7935C9CE98}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="8_{05125B79-E365-6E46-8F3D-67F167C30EE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9552DE81-0A8B-FC4B-ACDA-C3EC3776114D}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="000000KL" sheetId="2" r:id="rId1"/>
@@ -205,7 +205,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -217,6 +217,9 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -520,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="44" width="9.1640625" customWidth="1"/>
@@ -884,6 +887,14 @@
       </c>
       <c r="B45" s="2">
         <v>403.7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="6">
+        <v>2024</v>
+      </c>
+      <c r="B46" s="2">
+        <v>415.15</v>
       </c>
     </row>
   </sheetData>
@@ -917,6 +928,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8122317a-a166-4aca-8a73-cea3da482592">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4465cf7b-dff5-40ba-a744-c962d51df52a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000F48778665866F4D8347936C0218526D" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b64786a3cf0087cf934c39799665206d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8122317a-a166-4aca-8a73-cea3da482592" xmlns:ns3="4465cf7b-dff5-40ba-a744-c962d51df52a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="548e74e36a28f42524e46a5b3754702e" ns2:_="" ns3:_="">
     <xsd:import namespace="8122317a-a166-4aca-8a73-cea3da482592"/>
@@ -1105,34 +1136,46 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8122317a-a166-4aca-8a73-cea3da482592">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4465cf7b-dff5-40ba-a744-c962d51df52a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1876728-E984-471C-BB4B-A2D7B05C9B28}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{057EE4DA-AC09-4CFA-B46F-F562371825F9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="8122317a-a166-4aca-8a73-cea3da482592"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="4465cf7b-dff5-40ba-a744-c962d51df52a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A757BE5-88F5-4C09-A046-B2D05EACFF4C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A757BE5-88F5-4C09-A046-B2D05EACFF4C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{057EE4DA-AC09-4CFA-B46F-F562371825F9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1876728-E984-471C-BB4B-A2D7B05C9B28}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8122317a-a166-4aca-8a73-cea3da482592"/>
+    <ds:schemaRef ds:uri="4465cf7b-dff5-40ba-a744-c962d51df52a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/CPI.xlsx
+++ b/CPI.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29825"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -16,13 +16,35 @@
     <sheet name="000000KL" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>CPI</t>
+  </si>
+  <si>
     <t>1980</t>
   </si>
   <si>
@@ -153,19 +175,13 @@
   </si>
   <si>
     <t>2023</t>
-  </si>
-  <si>
-    <t>CPI</t>
-  </si>
-  <si>
-    <t>year</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -524,372 +540,372 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="44" width="9.1640625" customWidth="1"/>
+    <col min="1" max="44" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2" s="2">
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2">
         <v>112.1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2">
         <v>121.7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B5" s="2">
         <v>132.6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B6" s="2">
         <v>143.19999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B7" s="2">
         <v>153.80000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2">
         <v>160.30000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B9" s="2">
         <v>167</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B10" s="2">
         <v>176.7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B11" s="2">
         <v>188.1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B12" s="2">
         <v>207.8</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B13" s="2">
         <v>227.2</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B14" s="2">
         <v>232.4</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B15" s="2">
         <v>243.2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B16" s="2">
         <v>248.5</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B17" s="2">
         <v>254.8</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B18" s="2">
         <v>256</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B19" s="2">
         <v>257.3</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B20" s="2">
         <v>257</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B21" s="2">
         <v>258.10000000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B22" s="2">
         <v>260.7</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B23" s="2">
         <v>267.10000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B24" s="2">
         <v>272.8</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B25" s="2">
         <v>278.10000000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B26" s="2">
         <v>279.2</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B27" s="2">
         <v>280.39999999999998</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B28" s="2">
         <v>284.22000000000003</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B29" s="2">
         <v>290.51</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B30" s="2">
         <v>300.61</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B31" s="2">
         <v>299.66000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B32" s="2">
         <v>303.45999999999998</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B33" s="2">
         <v>311.43</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B34" s="2">
         <v>314.2</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B35" s="2">
         <v>314.06</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B36" s="2">
         <v>313.49</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B37" s="2">
         <v>313.35000000000002</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B38" s="2">
         <v>316.43</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B39" s="2">
         <v>322.11</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B40" s="2">
         <v>328.4</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B41" s="2">
         <v>334.26</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B42" s="2">
         <v>335.92</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B43" s="2">
         <v>343.19</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B44" s="2">
         <v>371.91</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B45" s="2">
         <v>403.7</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2">
       <c r="A46" s="6">
         <v>2024</v>
       </c>
@@ -906,20 +922,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C853E1D5-2AF6-F040-A3AB-B0ACB92A777A}">
   <dimension ref="E7:H13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="7" spans="5:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="5:8" ht="15.95">
       <c r="E7" s="3"/>
       <c r="H7" s="3"/>
     </row>
-    <row r="8" spans="5:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="5:8" ht="15.95">
       <c r="E8" s="3"/>
     </row>
-    <row r="11" spans="5:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="5:8" ht="15.95">
       <c r="E11" s="4"/>
       <c r="H11" s="4"/>
     </row>
-    <row r="13" spans="5:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="5:8" ht="15.95">
       <c r="E13" s="5"/>
     </row>
   </sheetData>
@@ -928,26 +944,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8122317a-a166-4aca-8a73-cea3da482592">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4465cf7b-dff5-40ba-a744-c962d51df52a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000F48778665866F4D8347936C0218526D" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b64786a3cf0087cf934c39799665206d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8122317a-a166-4aca-8a73-cea3da482592" xmlns:ns3="4465cf7b-dff5-40ba-a744-c962d51df52a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="548e74e36a28f42524e46a5b3754702e" ns2:_="" ns3:_="">
     <xsd:import namespace="8122317a-a166-4aca-8a73-cea3da482592"/>
@@ -1136,46 +1132,34 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8122317a-a166-4aca-8a73-cea3da482592">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4465cf7b-dff5-40ba-a744-c962d51df52a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{057EE4DA-AC09-4CFA-B46F-F562371825F9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="8122317a-a166-4aca-8a73-cea3da482592"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="4465cf7b-dff5-40ba-a744-c962d51df52a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1876728-E984-471C-BB4B-A2D7B05C9B28}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A757BE5-88F5-4C09-A046-B2D05EACFF4C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A757BE5-88F5-4C09-A046-B2D05EACFF4C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1876728-E984-471C-BB4B-A2D7B05C9B28}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="8122317a-a166-4aca-8a73-cea3da482592"/>
-    <ds:schemaRef ds:uri="4465cf7b-dff5-40ba-a744-c962d51df52a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{057EE4DA-AC09-4CFA-B46F-F562371825F9}"/>
 </file>